--- a/data/trans_orig/SE_ADU-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/SE_ADU-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sexo adulto elegido en 2007</t>
+          <t>Sexo adulto elegido en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,47 +768,47 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>258803</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
           <t>260838</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>99,22%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>260838</t>
-        </is>
-      </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>236394</t>
+          <t>236936</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>283813</t>
+          <t>285602</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>53,5%</t>
         </is>
       </c>
     </row>
@@ -846,82 +846,82 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>271084</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
           <t>273010</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>99,29%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2035</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>273010</t>
-        </is>
-      </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>250035</t>
+          <t>248246</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>297454</t>
+          <t>296912</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>55,62%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,47 +1111,47 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>502014</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
           <t>503949</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>99,62%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>499</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>503949</t>
-        </is>
-      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>472357</t>
+          <t>475405</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>532798</t>
+          <t>539574</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>54,12%</t>
         </is>
       </c>
     </row>
@@ -1189,82 +1189,82 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>491044</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>465</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
           <t>493075</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>99,59%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1935</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>465</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>493075</t>
-        </is>
-      </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>464226</t>
+          <t>457450</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>524667</t>
+          <t>521619</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,32%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,47 +1454,47 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>333496</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
           <t>335412</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>99,43%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>335412</t>
-        </is>
-      </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>310395</t>
+          <t>310871</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>359422</t>
+          <t>361147</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>55,2%</t>
         </is>
       </c>
     </row>
@@ -1532,82 +1532,82 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>316878</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
           <t>318846</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>99,38%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1916</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>318846</t>
-        </is>
-      </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>294836</t>
+          <t>293111</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>343863</t>
+          <t>343387</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>52,48%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,47 +1797,47 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>369604</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>384</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
           <t>371456</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>99,5%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>371456</t>
-        </is>
-      </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>343523</t>
+          <t>345776</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>397321</t>
+          <t>398441</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>54,57%</t>
         </is>
       </c>
     </row>
@@ -1875,82 +1875,82 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>356774</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
           <t>358671</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,47%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1852</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>362</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>358671</t>
-        </is>
-      </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>332806</t>
+          <t>331686</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>386604</t>
+          <t>384351</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>52,64%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,47 +2140,47 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>205666</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
           <t>207668</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>99,04%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>207668</t>
-        </is>
-      </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>185583</t>
+          <t>188472</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>227347</t>
+          <t>228806</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>55,67%</t>
         </is>
       </c>
     </row>
@@ -2218,82 +2218,82 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>201423</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
           <t>203308</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,07%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>203308</t>
-        </is>
-      </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>183629</t>
+          <t>182170</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>225393</t>
+          <t>222504</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>54,14%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,47 +2483,47 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>276174</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
           <t>278144</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>99,29%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>278144</t>
-        </is>
-      </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>252867</t>
+          <t>255263</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>300992</t>
+          <t>300488</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>54,74%</t>
         </is>
       </c>
     </row>
@@ -2561,82 +2561,82 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>268864</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
           <t>270811</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>99,28%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>270811</t>
-        </is>
-      </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>247963</t>
+          <t>248467</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>296088</t>
+          <t>293692</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>53,5%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,47 +2826,47 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>636249</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
           <t>638219</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>99,69%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>621</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>638219</t>
-        </is>
-      </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>603724</t>
+          <t>603637</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>674903</t>
+          <t>673692</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>53,76%</t>
         </is>
       </c>
     </row>
@@ -2904,82 +2904,82 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>613056</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
           <t>615027</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>99,68%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>615027</t>
-        </is>
-      </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>578343</t>
+          <t>579554</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>649522</t>
+          <t>649609</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,47 +3169,47 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>781494</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>745</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
           <t>783511</t>
         </is>
       </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>99,74%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>745</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>783511</t>
-        </is>
-      </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>743904</t>
+          <t>747987</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>824674</t>
+          <t>829007</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>48,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>54,28%</t>
         </is>
       </c>
     </row>
@@ -3247,82 +3247,82 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>741857</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>736</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
           <t>743795</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>99,74%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>736</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>743795</t>
-        </is>
-      </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>702632</t>
+          <t>698299</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>783402</t>
+          <t>779319</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,03%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,47 +3512,47 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3377229</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>3297</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
           <t>3379197</t>
         </is>
       </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>99,94%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>3297</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>3379197</t>
-        </is>
-      </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3299203</t>
+          <t>3299502</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3468302</t>
+          <t>3461675</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>52,01%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3274586</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3276543</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3187439</t>
+          <t>3194066</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3356538</t>
+          <t>3356239</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sexo adulto elegido en 2012</t>
+          <t>Sexo adulto elegido en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,47 +4091,47 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>285100</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
           <t>287245</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>287245</t>
-        </is>
-      </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>262557</t>
+          <t>260211</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>312890</t>
+          <t>311780</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,57%</t>
         </is>
       </c>
     </row>
@@ -4169,82 +4169,82 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>292739</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
           <t>294738</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2145</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>294738</t>
-        </is>
-      </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>269093</t>
+          <t>270203</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>319426</t>
+          <t>321772</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>55,29%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2052</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,47 +4434,47 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>521674</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
           <t>523765</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>99,6%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>523765</t>
-        </is>
-      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>490837</t>
+          <t>489487</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>553281</t>
+          <t>556620</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>54,08%</t>
         </is>
       </c>
     </row>
@@ -4512,82 +4512,82 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>503475</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>472</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
           <t>505527</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>99,59%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2091</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>472</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>505527</t>
-        </is>
-      </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>476011</t>
+          <t>472672</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>538455</t>
+          <t>539805</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,44%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,47 +4777,47 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>338962</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
           <t>341020</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>99,4%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>341020</t>
-        </is>
-      </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>315184</t>
+          <t>315805</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>366366</t>
+          <t>367347</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>55,23%</t>
         </is>
       </c>
     </row>
@@ -4855,82 +4855,82 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>322102</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
           <t>324046</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>99,4%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>2058</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>324046</t>
-        </is>
-      </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>298700</t>
+          <t>297719</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>349882</t>
+          <t>349261</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>52,52%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,47 +5120,47 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>386944</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
           <t>388951</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>388951</t>
-        </is>
-      </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>361878</t>
+          <t>361450</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>418610</t>
+          <t>415684</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,48%</t>
         </is>
       </c>
     </row>
@@ -5198,82 +5198,82 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>371901</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>344</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
           <t>373982</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,44%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>344</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>373982</t>
-        </is>
-      </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>344323</t>
+          <t>347249</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>401055</t>
+          <t>401483</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>52,62%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,47 +5463,47 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>217613</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
           <t>219591</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>219591</t>
-        </is>
-      </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>200876</t>
+          <t>198645</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>242295</t>
+          <t>240183</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>55,57%</t>
         </is>
       </c>
     </row>
@@ -5541,82 +5541,82 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>210547</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
           <t>212618</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,03%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>212618</t>
-        </is>
-      </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>189914</t>
+          <t>192026</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>231333</t>
+          <t>233564</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>54,04%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,47 +5806,47 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>278040</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
           <t>280031</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>99,29%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>280031</t>
-        </is>
-      </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>257648</t>
+          <t>257015</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>305200</t>
+          <t>304354</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>54,94%</t>
         </is>
       </c>
     </row>
@@ -5884,82 +5884,82 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>271974</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
           <t>273981</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>99,27%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1991</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>273981</t>
-        </is>
-      </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>248812</t>
+          <t>249658</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>296364</t>
+          <t>296997</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,61%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,47 +6149,47 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>691762</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
           <t>693853</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>99,7%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>636</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>693853</t>
-        </is>
-      </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>653456</t>
+          <t>653964</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>732998</t>
+          <t>732110</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>53,96%</t>
         </is>
       </c>
     </row>
@@ -6227,82 +6227,82 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>660732</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
           <t>662788</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>99,69%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>2091</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>618</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>662788</t>
-        </is>
-      </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>623643</t>
+          <t>624531</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>703185</t>
+          <t>702677</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>51,8%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,47 +6492,47 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>821766</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>757</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
           <t>823853</t>
         </is>
       </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>99,75%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>757</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>823853</t>
-        </is>
-      </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>782765</t>
+          <t>779852</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>863849</t>
+          <t>867347</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>54,11%</t>
         </is>
       </c>
     </row>
@@ -6570,82 +6570,82 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>777014</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
           <t>779098</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>2087</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>717</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>779098</t>
-        </is>
-      </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>739102</t>
+          <t>735604</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>820186</t>
+          <t>823099</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>51,35%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,47 +6835,47 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3556237</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>3298</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
           <t>3558309</t>
         </is>
       </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>99,94%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>3298</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>3558309</t>
-        </is>
-      </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3462499</t>
+          <t>3473059</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3637809</t>
+          <t>3648696</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>52,24%</t>
         </is>
       </c>
     </row>
@@ -6913,82 +6913,82 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3424729</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>3209</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
           <t>3426779</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>99,94%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>2072</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>3209</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>3426779</t>
-        </is>
-      </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3347279</t>
+          <t>3336392</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3522589</t>
+          <t>3512029</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,28%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sexo adulto elegido en 2016</t>
+          <t>Sexo adulto elegido en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,47 +7414,47 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>286710</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
           <t>288703</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>99,31%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>288703</t>
-        </is>
-      </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>264084</t>
+          <t>264490</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>313725</t>
+          <t>314960</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>54,07%</t>
         </is>
       </c>
     </row>
@@ -7492,82 +7492,82 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>291649</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
           <t>293761</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>99,28%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1993</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>293761</t>
-        </is>
-      </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>268739</t>
+          <t>267504</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>318380</t>
+          <t>317974</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,59%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,47 +7757,47 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>521013</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
           <t>523084</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>99,6%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>523084</t>
-        </is>
-      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>488905</t>
+          <t>490199</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>558242</t>
+          <t>555511</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,16%</t>
         </is>
       </c>
     </row>
@@ -7835,82 +7835,82 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>500548</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
           <t>502575</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>99,6%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2071</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>475</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>502575</t>
-        </is>
-      </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>467417</t>
+          <t>470148</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>536754</t>
+          <t>535460</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>52,21%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,47 +8100,47 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>334370</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
           <t>336309</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>99,42%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>336309</t>
-        </is>
-      </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>310164</t>
+          <t>311500</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>363618</t>
+          <t>362196</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>55,31%</t>
         </is>
       </c>
     </row>
@@ -8178,82 +8178,82 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>316745</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
           <t>318565</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>99,43%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1939</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>318565</t>
-        </is>
-      </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>291256</t>
+          <t>292678</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>344710</t>
+          <t>343374</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,43%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,47 +8443,47 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>385212</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
           <t>387283</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>99,47%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>358</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>387283</t>
-        </is>
-      </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>357379</t>
+          <t>360281</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>415124</t>
+          <t>416302</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>54,98%</t>
         </is>
       </c>
     </row>
@@ -8521,82 +8521,82 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>367963</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
           <t>369964</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,46%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2071</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>354</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>369964</t>
-        </is>
-      </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>342123</t>
+          <t>340945</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>399868</t>
+          <t>396966</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>52,42%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,47 +8786,47 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>216714</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
           <t>218587</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>99,14%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>218587</t>
-        </is>
-      </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>198167</t>
+          <t>197273</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>239252</t>
+          <t>239010</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>55,61%</t>
         </is>
       </c>
     </row>
@@ -8864,82 +8864,82 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>209318</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
           <t>211221</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>1873</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>211221</t>
-        </is>
-      </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>190556</t>
+          <t>190798</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>231641</t>
+          <t>232535</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>54,1%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,47 +9129,47 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>271130</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
           <t>273115</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>99,27%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>273115</t>
-        </is>
-      </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>248257</t>
+          <t>251501</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>295807</t>
+          <t>299931</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>55,93%</t>
         </is>
       </c>
     </row>
@@ -9207,82 +9207,82 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>261181</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
           <t>263123</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>99,26%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1985</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>263123</t>
-        </is>
-      </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>240431</t>
+          <t>236307</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>287981</t>
+          <t>284737</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,1%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2170</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,47 +9472,47 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>689242</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
           <t>691294</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>99,7%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>691294</t>
-        </is>
-      </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>656117</t>
+          <t>653567</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>730639</t>
+          <t>728736</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>54,07%</t>
         </is>
       </c>
     </row>
@@ -9550,82 +9550,82 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>654388</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
           <t>656558</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>99,67%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>2052</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>580</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>656558</t>
-        </is>
-      </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>617213</t>
+          <t>619116</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>691735</t>
+          <t>694285</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>51,51%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,47 +9815,47 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>824069</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>755</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
           <t>826167</t>
         </is>
       </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>99,75%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>755</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>826167</t>
-        </is>
-      </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>784701</t>
+          <t>784273</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>866495</t>
+          <t>866267</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>53,98%</t>
         </is>
       </c>
     </row>
@@ -9893,82 +9893,82 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>776592</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
           <t>778583</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>99,74%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>2098</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>750</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>778583</t>
-        </is>
-      </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>738255</t>
+          <t>738483</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>820049</t>
+          <t>820477</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>51,13%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,47 +10158,47 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3542503</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>3338</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
           <t>3544542</t>
         </is>
       </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>99,94%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>3338</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>3544542</t>
-        </is>
-      </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3466598</t>
+          <t>3459508</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3630980</t>
+          <t>3628134</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>52,29%</t>
         </is>
       </c>
     </row>
@@ -10236,82 +10236,82 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3392333</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
           <t>3394350</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>99,94%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>2039</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>3231</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>3394350</t>
-        </is>
-      </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3307912</t>
+          <t>3310758</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3472294</t>
+          <t>3479384</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>50,14%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sexo adulto elegido en 2023</t>
+          <t>Sexo adulto elegido en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1801</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>288603</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>263944</t>
+          <t>264239</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>312440</t>
+          <t>315298</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>52,46%</t>
         </is>
       </c>
     </row>
@@ -10815,82 +10815,82 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>309642</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
           <t>311443</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>99,42%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1032</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>311443</t>
-        </is>
-      </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>288637</t>
+          <t>285779</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>337133</t>
+          <t>336838</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>56,04%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2598</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,47 +11080,47 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>513592</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
           <t>514969</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>717</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>514969</t>
-        </is>
-      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>478134</t>
+          <t>477395</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>551175</t>
+          <t>549588</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>53,18%</t>
         </is>
       </c>
     </row>
@@ -11158,82 +11158,82 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>515792</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
           <t>518390</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>99,5%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1377</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>518390</t>
-        </is>
-      </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>482184</t>
+          <t>483771</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>555225</t>
+          <t>555964</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>53,8%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1681</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,47 +11423,47 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>347880</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>536</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
           <t>349128</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>99,64%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>536</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>349128</t>
-        </is>
-      </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>324299</t>
+          <t>324426</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>371166</t>
+          <t>373274</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>56,12%</t>
         </is>
       </c>
     </row>
@@ -11501,82 +11501,82 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>314369</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
           <t>316050</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>99,47%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1248</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>316050</t>
-        </is>
-      </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>294012</t>
+          <t>291904</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>340879</t>
+          <t>340752</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>51,23%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,47 +11766,47 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>474196</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>599</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
           <t>475718</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>99,68%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>599</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>475718</t>
-        </is>
-      </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>423980</t>
+          <t>431115</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>566623</t>
+          <t>564475</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>71,61%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>310510</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>221651</t>
+          <t>223799</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>364294</t>
+          <t>357159</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>45,31%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,47 +12109,47 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>257777</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
           <t>258779</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>99,61%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>495</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>258779</t>
-        </is>
-      </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>230858</t>
+          <t>229269</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>315256</t>
+          <t>311009</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>71,08%</t>
         </is>
       </c>
     </row>
@@ -12187,82 +12187,82 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>177517</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
           <t>178742</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,31%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>1002</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>178742</t>
-        </is>
-      </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>122265</t>
+          <t>126512</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>206663</t>
+          <t>208252</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,6%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1391</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,47 +12452,47 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>255985</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>460</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
           <t>257056</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>99,58%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>460</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>257056</t>
-        </is>
-      </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>238273</t>
+          <t>237838</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>277957</t>
+          <t>279177</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>53,01%</t>
         </is>
       </c>
     </row>
@@ -12530,82 +12530,82 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>268245</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
           <t>269636</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1071</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>269636</t>
-        </is>
-      </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>248735</t>
+          <t>247515</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>288419</t>
+          <t>288854</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>54,84%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,47 +12795,47 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>847568</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
           <t>849265</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>99,8%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>960</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>849265</t>
-        </is>
-      </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>731930</t>
+          <t>731903</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1075238</t>
+          <t>1069891</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12850,7 +12850,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>72,61%</t>
         </is>
       </c>
     </row>
@@ -12873,82 +12873,82 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>622281</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>599</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
           <t>624279</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>99,68%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>1697</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>599</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>624279</t>
-        </is>
-      </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>398306</t>
+          <t>403653</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>741614</t>
+          <t>741641</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,7 +12958,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,47 +13138,47 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>716434</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
           <t>717731</t>
         </is>
       </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>99,82%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>1062</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>717731</t>
-        </is>
-      </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>454038</t>
+          <t>443373</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>854605</t>
+          <t>857449</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>52,08%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>926383</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>791847</t>
+          <t>789003</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1192414</t>
+          <t>1203079</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>73,07%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,47 +13481,47 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3710952</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>5367</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
           <t>3712280</t>
         </is>
       </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>99,96%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>5367</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>3712280</t>
-        </is>
-      </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3347397</t>
+          <t>3360210</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4010183</t>
+          <t>3998706</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>55,75%</t>
         </is>
       </c>
     </row>
@@ -13559,82 +13559,82 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3457849</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>3376</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
           <t>3459817</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>99,94%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>1328</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>0,04%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>3376</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>3459817</t>
-        </is>
-      </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3161914</t>
+          <t>3173391</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3824700</t>
+          <t>3811887</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>53,15%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/SE_ADU-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/SE_ADU-Provincia-trans_orig.xlsx
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>236936</t>
+          <t>235676</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>285602</t>
+          <t>282949</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>53,0%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>248246</t>
+          <t>250899</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>296912</t>
+          <t>298172</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>55,85%</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>475405</t>
+          <t>471116</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>539574</t>
+          <t>535483</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>53,71%</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>457450</t>
+          <t>461541</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>521619</t>
+          <t>525908</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>52,75%</t>
         </is>
       </c>
     </row>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>310871</t>
+          <t>308771</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>361147</t>
+          <t>359238</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>54,91%</t>
         </is>
       </c>
     </row>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>293111</t>
+          <t>295020</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>343387</t>
+          <t>345487</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>52,81%</t>
         </is>
       </c>
     </row>
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>345776</t>
+          <t>345570</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>398441</t>
+          <t>396275</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,27%</t>
         </is>
       </c>
     </row>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>331686</t>
+          <t>333852</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>384351</t>
+          <t>384557</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,67%</t>
         </is>
       </c>
     </row>
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>188472</t>
+          <t>189104</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>228806</t>
+          <t>228607</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,63%</t>
         </is>
       </c>
     </row>
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>182170</t>
+          <t>182369</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>222504</t>
+          <t>221872</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>53,99%</t>
         </is>
       </c>
     </row>
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>255263</t>
+          <t>251259</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>300488</t>
+          <t>298522</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>54,38%</t>
         </is>
       </c>
     </row>
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>248467</t>
+          <t>250433</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>293692</t>
+          <t>297696</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>54,23%</t>
         </is>
       </c>
     </row>
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>603637</t>
+          <t>603366</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>673692</t>
+          <t>676067</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,95%</t>
         </is>
       </c>
     </row>
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>579554</t>
+          <t>577179</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>649609</t>
+          <t>649880</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>51,86%</t>
         </is>
       </c>
     </row>
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>747987</t>
+          <t>742144</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>829007</t>
+          <t>820432</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>53,72%</t>
         </is>
       </c>
     </row>
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>698299</t>
+          <t>706874</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>779319</t>
+          <t>785162</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>51,41%</t>
         </is>
       </c>
     </row>
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3299502</t>
+          <t>3291559</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3461675</t>
+          <t>3465110</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>52,06%</t>
         </is>
       </c>
     </row>
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3194066</t>
+          <t>3190631</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3356239</t>
+          <t>3364182</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,55%</t>
         </is>
       </c>
     </row>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>260211</t>
+          <t>263956</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>311780</t>
+          <t>311737</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>53,56%</t>
         </is>
       </c>
     </row>
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>270203</t>
+          <t>270246</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>321772</t>
+          <t>318027</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>54,65%</t>
         </is>
       </c>
     </row>
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>489487</t>
+          <t>492897</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>556620</t>
+          <t>556789</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>54,09%</t>
         </is>
       </c>
     </row>
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>472672</t>
+          <t>472503</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>539805</t>
+          <t>536395</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>52,11%</t>
         </is>
       </c>
     </row>
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>315805</t>
+          <t>312389</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>367347</t>
+          <t>365005</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>54,88%</t>
         </is>
       </c>
     </row>
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>297719</t>
+          <t>300061</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>349261</t>
+          <t>352677</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>53,03%</t>
         </is>
       </c>
     </row>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>361450</t>
+          <t>359467</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>415684</t>
+          <t>417083</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,67%</t>
         </is>
       </c>
     </row>
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>347249</t>
+          <t>345850</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>401483</t>
+          <t>403466</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,88%</t>
         </is>
       </c>
     </row>
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>198645</t>
+          <t>200480</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>240183</t>
+          <t>241718</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>55,93%</t>
         </is>
       </c>
     </row>
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>192026</t>
+          <t>190491</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>233564</t>
+          <t>231729</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>53,62%</t>
         </is>
       </c>
     </row>
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>257015</t>
+          <t>252595</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>304354</t>
+          <t>303665</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>54,81%</t>
         </is>
       </c>
     </row>
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>249658</t>
+          <t>250347</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>296997</t>
+          <t>301417</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>54,41%</t>
         </is>
       </c>
     </row>
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>653964</t>
+          <t>655602</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>732110</t>
+          <t>730442</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>53,84%</t>
         </is>
       </c>
     </row>
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>624531</t>
+          <t>626199</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>702677</t>
+          <t>701039</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>51,67%</t>
         </is>
       </c>
     </row>
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>779852</t>
+          <t>782745</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>867347</t>
+          <t>867706</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>54,13%</t>
         </is>
       </c>
     </row>
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>735604</t>
+          <t>735245</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>823099</t>
+          <t>820206</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,17%</t>
         </is>
       </c>
     </row>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3473059</t>
+          <t>3474644</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3648696</t>
+          <t>3647065</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>52,21%</t>
         </is>
       </c>
     </row>
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3336392</t>
+          <t>3338023</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3512029</t>
+          <t>3510444</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>50,26%</t>
         </is>
       </c>
     </row>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>264490</t>
+          <t>264130</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>314960</t>
+          <t>314642</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>54,02%</t>
         </is>
       </c>
     </row>
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>267504</t>
+          <t>267822</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>317974</t>
+          <t>318334</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>54,65%</t>
         </is>
       </c>
     </row>
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>490199</t>
+          <t>491872</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>555511</t>
+          <t>556523</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>54,26%</t>
         </is>
       </c>
     </row>
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>470148</t>
+          <t>469136</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>535460</t>
+          <t>533787</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>52,04%</t>
         </is>
       </c>
     </row>
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>311500</t>
+          <t>313159</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>362196</t>
+          <t>363404</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,49%</t>
         </is>
       </c>
     </row>
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>292678</t>
+          <t>291470</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>343374</t>
+          <t>341715</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>52,18%</t>
         </is>
       </c>
     </row>
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>360281</t>
+          <t>361314</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>416302</t>
+          <t>417659</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>55,15%</t>
         </is>
       </c>
     </row>
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>340945</t>
+          <t>339588</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>396966</t>
+          <t>395933</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>52,29%</t>
         </is>
       </c>
     </row>
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>197273</t>
+          <t>197007</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>239010</t>
+          <t>239970</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>55,83%</t>
         </is>
       </c>
     </row>
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>190798</t>
+          <t>189838</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>232535</t>
+          <t>232801</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>54,16%</t>
         </is>
       </c>
     </row>
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>251501</t>
+          <t>249225</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>299931</t>
+          <t>295331</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>55,07%</t>
         </is>
       </c>
     </row>
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>236307</t>
+          <t>240907</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>284737</t>
+          <t>287013</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>53,52%</t>
         </is>
       </c>
     </row>
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>653567</t>
+          <t>652815</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>728736</t>
+          <t>732372</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>54,34%</t>
         </is>
       </c>
     </row>
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>619116</t>
+          <t>615480</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>694285</t>
+          <t>695037</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,57%</t>
         </is>
       </c>
     </row>
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>784273</t>
+          <t>785720</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>866267</t>
+          <t>867075</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>54,03%</t>
         </is>
       </c>
     </row>
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>738483</t>
+          <t>737675</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>820477</t>
+          <t>819030</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>51,04%</t>
         </is>
       </c>
     </row>
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3459508</t>
+          <t>3458868</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3628134</t>
+          <t>3624708</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,24%</t>
         </is>
       </c>
     </row>
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3310758</t>
+          <t>3314184</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3479384</t>
+          <t>3480024</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>50,15%</t>
         </is>
       </c>
     </row>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>289634</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>264239</t>
+          <t>294279</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>315298</t>
+          <t>341186</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>53,74%</t>
         </is>
       </c>
     </row>
@@ -10810,7 +10810,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>285779</t>
+          <t>293720</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>336838</t>
+          <t>340627</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>53,65%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11075,7 +11075,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>477395</t>
+          <t>507946</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>549588</t>
+          <t>582465</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>50,74%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>54,08%</t>
         </is>
       </c>
     </row>
@@ -11153,7 +11153,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>483771</t>
+          <t>494676</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>555964</t>
+          <t>569195</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>52,84%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11418,7 +11418,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>324426</t>
+          <t>332375</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>373274</t>
+          <t>379501</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>53,0%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>56,44%</t>
         </is>
       </c>
     </row>
@@ -11496,7 +11496,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315994</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>291904</t>
+          <t>292874</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>340752</t>
+          <t>340000</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>50,57%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421962</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>431115</t>
+          <t>388497</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>564475</t>
+          <t>454602</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>57,17%</t>
         </is>
       </c>
     </row>
@@ -11839,7 +11839,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>312556</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>223799</t>
+          <t>340505</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>357159</t>
+          <t>406610</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>51,14%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228917</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>229269</t>
+          <t>213086</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>311009</t>
+          <t>245247</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>56,43%</t>
         </is>
       </c>
     </row>
@@ -12182,7 +12182,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>126512</t>
+          <t>189335</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>208252</t>
+          <t>221496</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>50,97%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12447,7 +12447,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>237838</t>
+          <t>244940</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>279177</t>
+          <t>283429</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>53,03%</t>
         </is>
       </c>
     </row>
@@ -12525,7 +12525,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>247515</t>
+          <t>251028</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>288854</t>
+          <t>289517</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>54,17%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>731903</t>
+          <t>728649</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1069891</t>
+          <t>813455</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>54,53%</t>
         </is>
       </c>
     </row>
@@ -12868,7 +12868,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>403653</t>
+          <t>678289</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>741641</t>
+          <t>763095</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>51,15%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13133,7 +13133,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>443373</t>
+          <t>793162</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>857449</t>
+          <t>874675</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>53,68%</t>
         </is>
       </c>
     </row>
@@ -13211,7 +13211,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>928721</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>789003</t>
+          <t>754728</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1203079</t>
+          <t>836241</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>51,32%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13476,7 +13476,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3360210</t>
+          <t>3647018</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3998706</t>
+          <t>3820432</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>52,55%</t>
         </is>
       </c>
     </row>
@@ -13554,7 +13554,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3173391</t>
+          <t>3449284</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3811887</t>
+          <t>3622698</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>49,83%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
